--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117972023</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>117971992</v>
       </c>
       <c r="B3" t="n">
-        <v>90519</v>
+        <v>90521</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118685896</v>
+        <v>118694532</v>
       </c>
       <c r="B4" t="n">
-        <v>90524</v>
+        <v>97821</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +920,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>219797</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574161</v>
+        <v>574135</v>
       </c>
       <c r="R4" t="n">
-        <v>6404755</v>
+        <v>6404760</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118685752</v>
+        <v>118685808</v>
       </c>
       <c r="B5" t="n">
         <v>97821</v>
@@ -1057,10 +1062,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1074,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574223</v>
+        <v>574195</v>
       </c>
       <c r="R5" t="n">
-        <v>6404773</v>
+        <v>6404746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1123,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>9 blommande, 5 sterila</t>
+          <t>4 blommande, 2 sterila</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1256,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118685808</v>
+        <v>118685896</v>
       </c>
       <c r="B7" t="n">
-        <v>97821</v>
+        <v>90524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,43 +1277,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219797</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574195</v>
+        <v>574161</v>
       </c>
       <c r="R7" t="n">
-        <v>6404746</v>
+        <v>6404755</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,11 +1352,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>4 blommande, 2 sterila</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,7 +1379,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118694532</v>
+        <v>118685752</v>
       </c>
       <c r="B8" t="n">
         <v>97821</v>
@@ -1415,14 +1414,10 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1436,13 +1431,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574135</v>
+        <v>574223</v>
       </c>
       <c r="R8" t="n">
-        <v>6404760</v>
+        <v>6404773</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,6 +1467,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118694532</v>
+        <v>118685752</v>
       </c>
       <c r="B4" t="n">
         <v>97821</v>
@@ -943,14 +943,10 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -964,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574135</v>
+        <v>574223</v>
       </c>
       <c r="R4" t="n">
-        <v>6404760</v>
+        <v>6404773</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,6 +996,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118685808</v>
+        <v>118694532</v>
       </c>
       <c r="B5" t="n">
         <v>97821</v>
@@ -1062,7 +1063,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,13 +1084,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574195</v>
+        <v>574135</v>
       </c>
       <c r="R5" t="n">
-        <v>6404746</v>
+        <v>6404760</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,11 +1120,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 blommande, 2 sterila</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118685860</v>
+        <v>118685808</v>
       </c>
       <c r="B6" t="n">
-        <v>90524</v>
+        <v>97821</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,38 +1159,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574172</v>
+        <v>574195</v>
       </c>
       <c r="R6" t="n">
-        <v>6404751</v>
+        <v>6404746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,6 +1239,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 blommande, 2 sterila</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1379,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118685752</v>
+        <v>118685860</v>
       </c>
       <c r="B8" t="n">
-        <v>97821</v>
+        <v>90524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,39 +1397,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219797</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1431,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574223</v>
+        <v>574172</v>
       </c>
       <c r="R8" t="n">
-        <v>6404773</v>
+        <v>6404751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,11 +1472,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118685752</v>
+        <v>118685896</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
+        <v>90531</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574223</v>
+        <v>574161</v>
       </c>
       <c r="R4" t="n">
-        <v>6404773</v>
+        <v>6404755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,11 +995,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118694532</v>
+        <v>118685752</v>
       </c>
       <c r="B5" t="n">
-        <v>97821</v>
+        <v>97828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,14 +1057,10 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1084,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574135</v>
+        <v>574223</v>
       </c>
       <c r="R5" t="n">
-        <v>6404760</v>
+        <v>6404773</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,6 +1110,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118685808</v>
+        <v>118685860</v>
       </c>
       <c r="B6" t="n">
-        <v>97821</v>
+        <v>90531</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,43 +1154,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219797</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574195</v>
+        <v>574172</v>
       </c>
       <c r="R6" t="n">
-        <v>6404746</v>
+        <v>6404751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,11 +1229,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 blommande, 2 sterila</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118685896</v>
+        <v>118694532</v>
       </c>
       <c r="B7" t="n">
-        <v>90524</v>
+        <v>97828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,38 +1268,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>219797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,13 +1312,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574161</v>
+        <v>574135</v>
       </c>
       <c r="R7" t="n">
-        <v>6404755</v>
+        <v>6404760</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118685860</v>
+        <v>118685808</v>
       </c>
       <c r="B8" t="n">
-        <v>90524</v>
+        <v>97828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,38 +1387,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>219797</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574172</v>
+        <v>574195</v>
       </c>
       <c r="R8" t="n">
-        <v>6404751</v>
+        <v>6404746</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,6 +1467,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 blommande, 2 sterila</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118685752</v>
+        <v>118685860</v>
       </c>
       <c r="B5" t="n">
-        <v>97828</v>
+        <v>90531</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,39 +1034,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574223</v>
+        <v>574172</v>
       </c>
       <c r="R5" t="n">
-        <v>6404773</v>
+        <v>6404751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,11 +1109,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118685860</v>
+        <v>118694532</v>
       </c>
       <c r="B6" t="n">
-        <v>90531</v>
+        <v>97828</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1148,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,13 +1192,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574172</v>
+        <v>574135</v>
       </c>
       <c r="R6" t="n">
-        <v>6404751</v>
+        <v>6404760</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118694532</v>
+        <v>118685808</v>
       </c>
       <c r="B7" t="n">
         <v>97828</v>
@@ -1291,7 +1290,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1312,13 +1311,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574135</v>
+        <v>574195</v>
       </c>
       <c r="R7" t="n">
-        <v>6404760</v>
+        <v>6404746</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,6 +1347,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 blommande, 2 sterila</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,7 +1379,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118685808</v>
+        <v>118685752</v>
       </c>
       <c r="B8" t="n">
         <v>97828</v>
@@ -1410,14 +1414,10 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574195</v>
+        <v>574223</v>
       </c>
       <c r="R8" t="n">
-        <v>6404746</v>
+        <v>6404773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4 blommande, 2 sterila</t>
+          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117971992</v>
       </c>
       <c r="B2" t="n">
-        <v>90524</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117972023</v>
+        <v>117971999</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,35 +795,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574153</v>
+        <v>574157</v>
       </c>
       <c r="R3" t="n">
-        <v>6404727</v>
+        <v>6404774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,17 +868,13 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,55 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118694532</v>
+        <v>118685860</v>
       </c>
       <c r="B4" t="n">
-        <v>97833</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574135</v>
+        <v>574172</v>
       </c>
       <c r="R4" t="n">
-        <v>6404760</v>
+        <v>6404751</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,51 +1002,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118685752</v>
+        <v>118685896</v>
       </c>
       <c r="B5" t="n">
-        <v>97833</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574223</v>
+        <v>574161</v>
       </c>
       <c r="R5" t="n">
-        <v>6404773</v>
+        <v>6404755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118685808</v>
+        <v>117972023</v>
       </c>
       <c r="B6" t="n">
-        <v>97833</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,39 +1122,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574195</v>
+        <v>574153</v>
       </c>
       <c r="R6" t="n">
-        <v>6404746</v>
+        <v>6404727</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,17 +1188,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 blommande, 2 sterila</t>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,37 +1225,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118685896</v>
+        <v>117972180</v>
       </c>
       <c r="B7" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1309,12 +1258,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574161</v>
+        <v>574246</v>
       </c>
       <c r="R7" t="n">
-        <v>6404755</v>
+        <v>6404762</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,12 +1302,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1321,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,50 +1339,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118685860</v>
+        <v>126651231</v>
       </c>
       <c r="B8" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>102020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574172</v>
+        <v>574053</v>
       </c>
       <c r="R8" t="n">
-        <v>6404751</v>
+        <v>6404773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,12 +1417,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,12 +1453,7 @@
         <v>118752833</v>
       </c>
       <c r="B9" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,6 +1561,354 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118685752</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>574223</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6404773</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>9 blommande, 5 sterila</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118685808</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>574195</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6404746</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4 blommande, 2 sterila</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118694532</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>574135</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6404760</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,45 +1374,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126651231</v>
+        <v>135474230</v>
       </c>
       <c r="B8" t="n">
-        <v>45046</v>
+        <v>9415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102020</v>
+        <v>101246</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>funnen död</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1422,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574053</v>
+        <v>574131</v>
       </c>
       <c r="R8" t="n">
-        <v>6404773</v>
+        <v>6404769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,12 +1456,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vägkanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,7 +1475,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1484,50 +1492,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126651231</t>
+          <t>https://artportalen.se/Sighting/135474230</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118752833</v>
+        <v>126651231</v>
       </c>
       <c r="B9" t="n">
-        <v>58112</v>
+        <v>45046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>102020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1537,13 +1546,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574092</v>
+        <v>574053</v>
       </c>
       <c r="R9" t="n">
-        <v>6404756</v>
+        <v>6404773</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,17 +1576,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Utflugen kull</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,6 +1590,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1603,52 +1608,52 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118752833</t>
+          <t>https://artportalen.se/Sighting/126651231</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118685752</v>
+        <v>118752833</v>
       </c>
       <c r="B10" t="n">
-        <v>99093</v>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219797</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1656,13 +1661,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574223</v>
+        <v>574092</v>
       </c>
       <c r="R10" t="n">
-        <v>6404773</v>
+        <v>6404756</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,17 +1691,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>9 blommande, 5 sterila</t>
+          <t>Utflugen kull</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,7 +1710,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1723,56 +1727,52 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118685752</t>
+          <t>https://artportalen.se/Sighting/118752833</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118685808</v>
+        <v>135474406</v>
       </c>
       <c r="B11" t="n">
-        <v>99093</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219797</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574195</v>
+        <v>574162</v>
       </c>
       <c r="R11" t="n">
-        <v>6404746</v>
+        <v>6404755</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1810,17 +1810,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4 blommande, 2 sterila</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,7 +1824,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,13 +1841,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118685808</t>
+          <t>https://artportalen.se/Sighting/135474406</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118694532</v>
+        <v>118685752</v>
       </c>
       <c r="B12" t="n">
         <v>99093</v>
@@ -1883,14 +1877,10 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1904,13 +1894,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574135</v>
+        <v>574223</v>
       </c>
       <c r="R12" t="n">
-        <v>6404760</v>
+        <v>6404773</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1940,6 +1930,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>9 blommande, 5 sterila</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,7 +1961,612 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/118685752</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118685808</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>574195</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6404746</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4 blommande, 2 sterila</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118685808</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118694532</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>574135</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6404760</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/118694532</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135474285</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99249</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>574209</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6404750</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474285</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135474322</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99249</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>574195</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6404747</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>5 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474322</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135474345</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99249</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 20366, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>574220</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6404759</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>5 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474345</t>
         </is>
       </c>
     </row>
@@ -1983,6 +2583,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>135474285</v>
       </c>
       <c r="B15" t="n">
-        <v>99249</v>
+        <v>99251</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135474322</v>
       </c>
       <c r="B16" t="n">
-        <v>99249</v>
+        <v>99251</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99249</v>
+        <v>99251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>135474230</v>
       </c>
       <c r="B8" t="n">
-        <v>9415</v>
+        <v>9417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>135474406</v>
       </c>
       <c r="B11" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135474285</v>
       </c>
       <c r="B15" t="n">
-        <v>99251</v>
+        <v>99268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135474322</v>
       </c>
       <c r="B16" t="n">
-        <v>99251</v>
+        <v>99268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99251</v>
+        <v>99268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>135474285</v>
       </c>
       <c r="B15" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>135474322</v>
       </c>
       <c r="B16" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
